--- a/output/ols_model_summary.xlsx
+++ b/output/ols_model_summary.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-04-15 15:42</t>
+          <t>2026-04-17 05:03</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/output/ols_model_summary.xlsx
+++ b/output/ols_model_summary.xlsx
@@ -464,7 +464,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.678</t>
+          <t>0.710</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>399.1457</t>
+          <t>392.8205</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-04-17 05:03</t>
+          <t>2026-04-28 06:58</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -514,7 +514,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>411.9462</t>
+          <t>405.6210</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-192.57</t>
+          <t>-189.41</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>19.36</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.81e-09</t>
+          <t>2.58e-10</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>0.749</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>298.85</t>
+          <t>260.46</t>
         </is>
       </c>
     </row>
@@ -671,22 +671,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.96478358371174</v>
+        <v>8.503033612276692</v>
       </c>
       <c r="C2" t="n">
-        <v>15.11656764923609</v>
+        <v>14.11219890529535</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7253487589337676</v>
+        <v>0.6025307373669514</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4725682816723931</v>
+        <v>0.5503085343213414</v>
       </c>
       <c r="F2" t="n">
-        <v>-19.61136054251953</v>
+        <v>-20.04158297521693</v>
       </c>
       <c r="G2" t="n">
-        <v>41.54092770994301</v>
+        <v>37.04765019977031</v>
       </c>
     </row>
     <row r="3">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-1.42547903728297</v>
+        <v>-1.484960055635201</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3018062035426516</v>
+        <v>0.281753720426157</v>
       </c>
       <c r="D3" t="n">
-        <v>-4.723160162218202</v>
+        <v>-5.270418624425529</v>
       </c>
       <c r="E3" t="n">
-        <v>2.987830159829241e-05</v>
+        <v>5.318226319293269e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.035939704799458</v>
+        <v>-2.054860747627765</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.8150183697664825</v>
+        <v>-0.9150593636426377</v>
       </c>
     </row>
     <row r="4">
@@ -721,22 +721,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04462157321518934</v>
+        <v>0.04362646705239143</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01431537905049815</v>
+        <v>0.0133642425485085</v>
       </c>
       <c r="D4" t="n">
-        <v>3.11703749218129</v>
+        <v>3.264417485243884</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00342332066357833</v>
+        <v>0.002287156903596395</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01566598599286226</v>
+        <v>0.01659473499635435</v>
       </c>
       <c r="G4" t="n">
-        <v>0.07357716043751641</v>
+        <v>0.07065819910842851</v>
       </c>
     </row>
     <row r="5">
@@ -746,22 +746,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.908851670202455</v>
+        <v>-0.386683426003839</v>
       </c>
       <c r="C5" t="n">
-        <v>5.105681099089144</v>
+        <v>4.766451544375163</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3738681741292058</v>
+        <v>-0.08112605832742806</v>
       </c>
       <c r="E5" t="n">
-        <v>0.710527284260112</v>
+        <v>0.9357566096591186</v>
       </c>
       <c r="F5" t="n">
-        <v>-12.23606646993337</v>
+        <v>-10.02774168560667</v>
       </c>
       <c r="G5" t="n">
-        <v>8.418363129528462</v>
+        <v>9.254374833598998</v>
       </c>
     </row>
     <row r="6">
@@ -771,22 +771,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.981672098065419</v>
+        <v>7.516382347987886</v>
       </c>
       <c r="C6" t="n">
-        <v>2.174158380450667</v>
+        <v>2.02970384736016</v>
       </c>
       <c r="D6" t="n">
-        <v>3.671154856901892</v>
+        <v>3.70319165417345</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0007218141192743517</v>
+        <v>0.0006576478257091248</v>
       </c>
       <c r="F6" t="n">
-        <v>3.584021683206026</v>
+        <v>3.410918805568811</v>
       </c>
       <c r="G6" t="n">
-        <v>12.37932251292481</v>
+        <v>11.62184589040696</v>
       </c>
     </row>
     <row r="7">
@@ -796,22 +796,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1.607372923972505</v>
+        <v>-0.8929344032543534</v>
       </c>
       <c r="C7" t="n">
-        <v>2.647334604792689</v>
+        <v>2.47144149244712</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.607166514222473</v>
+        <v>-0.3613010487940811</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5472593759651506</v>
+        <v>0.7198244155709776</v>
       </c>
       <c r="F7" t="n">
-        <v>-6.962112591385782</v>
+        <v>-5.891896669429242</v>
       </c>
       <c r="G7" t="n">
-        <v>3.747366743440772</v>
+        <v>4.106027862920536</v>
       </c>
     </row>
     <row r="8">
@@ -821,22 +821,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.102143994929482</v>
+        <v>0.1037079874301129</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0144909865177634</v>
+        <v>0.01352818237696735</v>
       </c>
       <c r="D8" t="n">
-        <v>7.048795111655885</v>
+        <v>7.666069582761009</v>
       </c>
       <c r="E8" t="n">
-        <v>1.836964274600883e-08</v>
+        <v>2.656086872573239e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07283320807762685</v>
+        <v>0.07634465577161974</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1314547817813371</v>
+        <v>0.1310713190886061</v>
       </c>
     </row>
   </sheetData>
